--- a/docs/ia/benchmarks/olympics_raci_fbw_gap.xlsx
+++ b/docs/ia/benchmarks/olympics_raci_fbw_gap.xlsx
@@ -108,7 +108,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -210,6 +210,11 @@
         <fgColor rgb="00D8F0D8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C7D2FE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -251,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -362,6 +367,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -22650,7 +22658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L140"/>
+  <dimension ref="A1:L262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23159,7 +23167,7 @@
       </c>
       <c r="L8" s="27" t="inlineStr">
         <is>
-          <t>/console/venues</t>
+          <t>/console/venues + /console/venues/[venueId]</t>
         </is>
       </c>
     </row>
@@ -24647,7 +24655,7 @@
       </c>
       <c r="L32" s="27" t="inlineStr">
         <is>
-          <t>/console/safety/safeguarding + /m/safeguarding + /p/[slug]/athlete/safeguarding</t>
+          <t>/console/safety/safeguarding + /m/safeguarding + /p/[slug]/athlete/safeguarding + /p/[slug]/athlete/privacy + /p/[slug]/athlete/training + /p/[slug]/athlete/visa + /p/[slug]/athlete</t>
         </is>
       </c>
     </row>
@@ -24709,7 +24717,7 @@
       </c>
       <c r="L33" s="30" t="inlineStr">
         <is>
-          <t>/console/participants/delegations + /p/[slug]/delegation</t>
+          <t>/console/participants/delegations + /p/[slug]/delegation + /p/[slug]/delegation/accommodation</t>
         </is>
       </c>
     </row>
@@ -25143,7 +25151,7 @@
       </c>
       <c r="L40" s="27" t="inlineStr">
         <is>
-          <t>/console/accreditation/scans + /m/gate</t>
+          <t>/console/accreditation/scans + /m/gate + /m/gate/scan</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25585,7 @@
       </c>
       <c r="L47" s="30" t="inlineStr">
         <is>
-          <t>/console/safety/major-incident + /m/incident</t>
+          <t>/console/safety/major-incident + /m/incident + /m/incident/new</t>
         </is>
       </c>
     </row>
@@ -25701,7 +25709,7 @@
       </c>
       <c r="L49" s="30" t="inlineStr">
         <is>
-          <t>/console/transport/dispatch + /m/driver + /p/[slug]/delegation/transport</t>
+          <t>/console/transport/dispatch + /m/driver + /p/[slug]/delegation/transport + /m/driver/run/[runId]</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26453,7 @@
       </c>
       <c r="L61" s="30" t="inlineStr">
         <is>
-          <t>/console/safety/medical + /m/medic</t>
+          <t>/console/safety/medical + /m/medic + /m/medic/new + /console/safety/medical/encounters</t>
         </is>
       </c>
     </row>
@@ -27995,7 +28003,7 @@
       </c>
       <c r="L86" s="27" t="inlineStr">
         <is>
-          <t>/console/programs/ceremonies + /m/ros</t>
+          <t>/console/programs/ceremonies + /m/ros + /m/ros/[showId]</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28127,7 @@
       </c>
       <c r="L88" s="27" t="inlineStr">
         <is>
-          <t>/console/programs/protocol + /p/[slug]/vip</t>
+          <t>/console/programs/protocol + /p/[slug]/vip + /p/[slug]/vip/itinerary</t>
         </is>
       </c>
     </row>
@@ -28615,7 +28623,7 @@
       </c>
       <c r="L96" s="27" t="inlineStr">
         <is>
-          <t>/console/commercial/hospitality + /p/[slug]/hospitality</t>
+          <t>/console/commercial/hospitality + /p/[slug]/hospitality + /p/[slug]/hospitality/guests + /p/[slug]/hospitality/itinerary</t>
         </is>
       </c>
     </row>
@@ -29297,7 +29305,7 @@
       </c>
       <c r="L107" s="30" t="inlineStr">
         <is>
-          <t>/console/workforce/volunteers + /p/[slug]/volunteer + /m/shift</t>
+          <t>/console/workforce/volunteers + /p/[slug]/volunteer + /m/shift + /p/[slug]/volunteer/application</t>
         </is>
       </c>
     </row>
@@ -29607,7 +29615,7 @@
       </c>
       <c r="L112" s="27" t="inlineStr">
         <is>
-          <t>/console/workforce/rosters + /p/[slug]/volunteer/schedule + /m/shift</t>
+          <t>/console/workforce/rosters + /p/[slug]/volunteer/schedule + /m/shift + /m/shift/swap</t>
         </is>
       </c>
     </row>
@@ -31344,6 +31352,7570 @@
       <c r="L140" s="37" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="30" t="inlineStr">
+        <is>
+          <t>PF-001</t>
+        </is>
+      </c>
+      <c r="B141" s="30" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="C141" s="30" t="inlineStr">
+        <is>
+          <t>Projects lifecycle</t>
+        </is>
+      </c>
+      <c r="D141" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E141" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F141" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G141" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H141" s="30" t="inlineStr">
+        <is>
+          <t>Project records</t>
+        </is>
+      </c>
+      <c r="I141" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J141" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K141" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L141" s="30" t="inlineStr">
+        <is>
+          <t>/console/projects + /console/projects/new + /console/projects/[projectId] (all sub-tabs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="30" t="inlineStr">
+        <is>
+          <t>PF-002</t>
+        </is>
+      </c>
+      <c r="B142" s="30" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="C142" s="30" t="inlineStr">
+        <is>
+          <t>Tasks &amp; assignment</t>
+        </is>
+      </c>
+      <c r="D142" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E142" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F142" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G142" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H142" s="30" t="inlineStr">
+        <is>
+          <t>Task records</t>
+        </is>
+      </c>
+      <c r="I142" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J142" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K142" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L142" s="30" t="inlineStr">
+        <is>
+          <t>/console/tasks + /console/tasks/new + /console/tasks/[taskId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="30" t="inlineStr">
+        <is>
+          <t>PF-003</t>
+        </is>
+      </c>
+      <c r="B143" s="30" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="C143" s="30" t="inlineStr">
+        <is>
+          <t>Events calendar</t>
+        </is>
+      </c>
+      <c r="D143" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E143" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F143" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G143" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H143" s="30" t="inlineStr">
+        <is>
+          <t>Event records</t>
+        </is>
+      </c>
+      <c r="I143" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J143" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K143" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L143" s="30" t="inlineStr">
+        <is>
+          <t>/console/events + /console/events/new + /console/events/[eventId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="30" t="inlineStr">
+        <is>
+          <t>PF-004</t>
+        </is>
+      </c>
+      <c r="B144" s="30" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="C144" s="30" t="inlineStr">
+        <is>
+          <t>Canonical locations</t>
+        </is>
+      </c>
+      <c r="D144" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E144" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F144" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G144" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H144" s="30" t="inlineStr">
+        <is>
+          <t>Location records</t>
+        </is>
+      </c>
+      <c r="I144" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J144" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K144" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L144" s="30" t="inlineStr">
+        <is>
+          <t>/console/locations + /console/locations/new + /console/locations/[locationId] + /console/locations/picker</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="30" t="inlineStr">
+        <is>
+          <t>PF-005</t>
+        </is>
+      </c>
+      <c r="B145" s="30" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="C145" s="30" t="inlineStr">
+        <is>
+          <t>Master schedule (ICS)</t>
+        </is>
+      </c>
+      <c r="D145" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E145" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F145" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G145" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H145" s="30" t="inlineStr">
+        <is>
+          <t>Schedule feed</t>
+        </is>
+      </c>
+      <c r="I145" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J145" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K145" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L145" s="30" t="inlineStr">
+        <is>
+          <t>/console/schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="30" t="inlineStr">
+        <is>
+          <t>PF-006</t>
+        </is>
+      </c>
+      <c r="B146" s="30" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C146" s="30" t="inlineStr">
+        <is>
+          <t>Pipeline / CRM</t>
+        </is>
+      </c>
+      <c r="D146" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E146" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F146" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G146" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H146" s="30" t="inlineStr">
+        <is>
+          <t>Deal records</t>
+        </is>
+      </c>
+      <c r="I146" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J146" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K146" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L146" s="30" t="inlineStr">
+        <is>
+          <t>/console/pipeline + /console/pipeline/[dealId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="30" t="inlineStr">
+        <is>
+          <t>PF-007</t>
+        </is>
+      </c>
+      <c r="B147" s="30" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C147" s="30" t="inlineStr">
+        <is>
+          <t>Lead management</t>
+        </is>
+      </c>
+      <c r="D147" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E147" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F147" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G147" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H147" s="30" t="inlineStr">
+        <is>
+          <t>Lead records</t>
+        </is>
+      </c>
+      <c r="I147" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J147" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K147" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L147" s="30" t="inlineStr">
+        <is>
+          <t>/console/leads + /console/leads/new + /console/leads/[leadId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="30" t="inlineStr">
+        <is>
+          <t>PF-008</t>
+        </is>
+      </c>
+      <c r="B148" s="30" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C148" s="30" t="inlineStr">
+        <is>
+          <t>Client directory</t>
+        </is>
+      </c>
+      <c r="D148" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E148" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F148" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G148" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H148" s="30" t="inlineStr">
+        <is>
+          <t>Client records</t>
+        </is>
+      </c>
+      <c r="I148" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J148" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K148" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L148" s="30" t="inlineStr">
+        <is>
+          <t>/console/clients + /console/clients/new + /console/clients/[clientId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="30" t="inlineStr">
+        <is>
+          <t>PF-009</t>
+        </is>
+      </c>
+      <c r="B149" s="30" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C149" s="30" t="inlineStr">
+        <is>
+          <t>Proposals</t>
+        </is>
+      </c>
+      <c r="D149" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E149" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F149" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G149" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H149" s="30" t="inlineStr">
+        <is>
+          <t>Proposal records</t>
+        </is>
+      </c>
+      <c r="I149" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J149" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K149" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L149" s="30" t="inlineStr">
+        <is>
+          <t>/console/proposals + /console/proposals/new + /console/proposals/[proposalId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="30" t="inlineStr">
+        <is>
+          <t>PF-010</t>
+        </is>
+      </c>
+      <c r="B150" s="30" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C150" s="30" t="inlineStr">
+        <is>
+          <t>Finance hub</t>
+        </is>
+      </c>
+      <c r="D150" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E150" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F150" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G150" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H150" s="30" t="inlineStr">
+        <is>
+          <t>Finance dashboard</t>
+        </is>
+      </c>
+      <c r="I150" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J150" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K150" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L150" s="30" t="inlineStr">
+        <is>
+          <t>/console/finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="30" t="inlineStr">
+        <is>
+          <t>PF-011</t>
+        </is>
+      </c>
+      <c r="B151" s="30" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C151" s="30" t="inlineStr">
+        <is>
+          <t>Invoicing</t>
+        </is>
+      </c>
+      <c r="D151" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E151" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F151" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G151" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H151" s="30" t="inlineStr">
+        <is>
+          <t>Invoice records</t>
+        </is>
+      </c>
+      <c r="I151" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J151" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K151" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L151" s="30" t="inlineStr">
+        <is>
+          <t>/console/finance/invoices + /console/finance/invoices/[invoiceId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="30" t="inlineStr">
+        <is>
+          <t>PF-012</t>
+        </is>
+      </c>
+      <c r="B152" s="30" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C152" s="30" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="D152" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E152" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F152" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G152" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H152" s="30" t="inlineStr">
+        <is>
+          <t>Expense records</t>
+        </is>
+      </c>
+      <c r="I152" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J152" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K152" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L152" s="30" t="inlineStr">
+        <is>
+          <t>/console/finance/expenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="30" t="inlineStr">
+        <is>
+          <t>PF-013</t>
+        </is>
+      </c>
+      <c r="B153" s="30" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C153" s="30" t="inlineStr">
+        <is>
+          <t>Budgets</t>
+        </is>
+      </c>
+      <c r="D153" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E153" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F153" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G153" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H153" s="30" t="inlineStr">
+        <is>
+          <t>Budget records</t>
+        </is>
+      </c>
+      <c r="I153" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J153" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K153" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L153" s="30" t="inlineStr">
+        <is>
+          <t>/console/finance/budgets</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="30" t="inlineStr">
+        <is>
+          <t>PF-014</t>
+        </is>
+      </c>
+      <c r="B154" s="30" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C154" s="30" t="inlineStr">
+        <is>
+          <t>Time tracking</t>
+        </is>
+      </c>
+      <c r="D154" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E154" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F154" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G154" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H154" s="30" t="inlineStr">
+        <is>
+          <t>Time records</t>
+        </is>
+      </c>
+      <c r="I154" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J154" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K154" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L154" s="30" t="inlineStr">
+        <is>
+          <t>/console/finance/time</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="30" t="inlineStr">
+        <is>
+          <t>PF-015</t>
+        </is>
+      </c>
+      <c r="B155" s="30" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C155" s="30" t="inlineStr">
+        <is>
+          <t>Mileage</t>
+        </is>
+      </c>
+      <c r="D155" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E155" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F155" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G155" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H155" s="30" t="inlineStr">
+        <is>
+          <t>Mileage records</t>
+        </is>
+      </c>
+      <c r="I155" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J155" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K155" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L155" s="30" t="inlineStr">
+        <is>
+          <t>/console/finance/mileage</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="30" t="inlineStr">
+        <is>
+          <t>PF-016</t>
+        </is>
+      </c>
+      <c r="B156" s="30" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C156" s="30" t="inlineStr">
+        <is>
+          <t>Advances</t>
+        </is>
+      </c>
+      <c r="D156" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E156" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F156" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G156" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H156" s="30" t="inlineStr">
+        <is>
+          <t>Advance records</t>
+        </is>
+      </c>
+      <c r="I156" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J156" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K156" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L156" s="30" t="inlineStr">
+        <is>
+          <t>/console/finance/advances</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="30" t="inlineStr">
+        <is>
+          <t>PF-017</t>
+        </is>
+      </c>
+      <c r="B157" s="30" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C157" s="30" t="inlineStr">
+        <is>
+          <t>Payouts</t>
+        </is>
+      </c>
+      <c r="D157" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E157" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F157" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G157" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H157" s="30" t="inlineStr">
+        <is>
+          <t>Payout records</t>
+        </is>
+      </c>
+      <c r="I157" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J157" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K157" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L157" s="30" t="inlineStr">
+        <is>
+          <t>/console/finance/payouts</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="30" t="inlineStr">
+        <is>
+          <t>PF-018</t>
+        </is>
+      </c>
+      <c r="B158" s="30" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C158" s="30" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="D158" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E158" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F158" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G158" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H158" s="30" t="inlineStr">
+        <is>
+          <t>Report views</t>
+        </is>
+      </c>
+      <c r="I158" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J158" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K158" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L158" s="30" t="inlineStr">
+        <is>
+          <t>/console/finance/reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="30" t="inlineStr">
+        <is>
+          <t>PF-019</t>
+        </is>
+      </c>
+      <c r="B159" s="30" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C159" s="30" t="inlineStr">
+        <is>
+          <t>Treasury / FX</t>
+        </is>
+      </c>
+      <c r="D159" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E159" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F159" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G159" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H159" s="30" t="inlineStr">
+        <is>
+          <t>Treasury dashboard</t>
+        </is>
+      </c>
+      <c r="I159" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J159" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K159" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L159" s="30" t="inlineStr">
+        <is>
+          <t>/console/finance/treasury</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="30" t="inlineStr">
+        <is>
+          <t>PF-020</t>
+        </is>
+      </c>
+      <c r="B160" s="30" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C160" s="30" t="inlineStr">
+        <is>
+          <t>Procurement hub</t>
+        </is>
+      </c>
+      <c r="D160" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E160" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F160" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G160" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H160" s="30" t="inlineStr">
+        <is>
+          <t>Procurement dashboard</t>
+        </is>
+      </c>
+      <c r="I160" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J160" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K160" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L160" s="30" t="inlineStr">
+        <is>
+          <t>/console/procurement</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="30" t="inlineStr">
+        <is>
+          <t>PF-021</t>
+        </is>
+      </c>
+      <c r="B161" s="30" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C161" s="30" t="inlineStr">
+        <is>
+          <t>Requisitions</t>
+        </is>
+      </c>
+      <c r="D161" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E161" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F161" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G161" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H161" s="30" t="inlineStr">
+        <is>
+          <t>Req records</t>
+        </is>
+      </c>
+      <c r="I161" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J161" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K161" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L161" s="30" t="inlineStr">
+        <is>
+          <t>/console/procurement/requisitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="30" t="inlineStr">
+        <is>
+          <t>PF-022</t>
+        </is>
+      </c>
+      <c r="B162" s="30" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C162" s="30" t="inlineStr">
+        <is>
+          <t>Purchase orders</t>
+        </is>
+      </c>
+      <c r="D162" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E162" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F162" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G162" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H162" s="30" t="inlineStr">
+        <is>
+          <t>PO records</t>
+        </is>
+      </c>
+      <c r="I162" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J162" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K162" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L162" s="30" t="inlineStr">
+        <is>
+          <t>/console/procurement/purchase-orders + /console/procurement/purchase-orders/[poId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="30" t="inlineStr">
+        <is>
+          <t>PF-023</t>
+        </is>
+      </c>
+      <c r="B163" s="30" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C163" s="30" t="inlineStr">
+        <is>
+          <t>Vendor directory</t>
+        </is>
+      </c>
+      <c r="D163" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E163" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F163" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G163" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H163" s="30" t="inlineStr">
+        <is>
+          <t>Vendor records</t>
+        </is>
+      </c>
+      <c r="I163" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J163" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K163" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L163" s="30" t="inlineStr">
+        <is>
+          <t>/console/procurement/vendors</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="30" t="inlineStr">
+        <is>
+          <t>PF-024</t>
+        </is>
+      </c>
+      <c r="B164" s="30" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C164" s="30" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="D164" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E164" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F164" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G164" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H164" s="30" t="inlineStr">
+        <is>
+          <t>Catalog entries</t>
+        </is>
+      </c>
+      <c r="I164" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J164" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K164" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L164" s="30" t="inlineStr">
+        <is>
+          <t>/console/procurement/catalog</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="30" t="inlineStr">
+        <is>
+          <t>PF-025</t>
+        </is>
+      </c>
+      <c r="B165" s="30" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C165" s="30" t="inlineStr">
+        <is>
+          <t>RFQs</t>
+        </is>
+      </c>
+      <c r="D165" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E165" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F165" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G165" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H165" s="30" t="inlineStr">
+        <is>
+          <t>RFQ records</t>
+        </is>
+      </c>
+      <c r="I165" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J165" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K165" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L165" s="30" t="inlineStr">
+        <is>
+          <t>/console/procurement/rfqs + /console/procurement/rfqs/new + /console/procurement/rfqs/[rfqId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="30" t="inlineStr">
+        <is>
+          <t>PF-026</t>
+        </is>
+      </c>
+      <c r="B166" s="30" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C166" s="30" t="inlineStr">
+        <is>
+          <t>Sourcing events</t>
+        </is>
+      </c>
+      <c r="D166" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E166" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F166" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G166" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H166" s="30" t="inlineStr">
+        <is>
+          <t>Sourcing records</t>
+        </is>
+      </c>
+      <c r="I166" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J166" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K166" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L166" s="30" t="inlineStr">
+        <is>
+          <t>/console/procurement/sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="30" t="inlineStr">
+        <is>
+          <t>PF-027</t>
+        </is>
+      </c>
+      <c r="B167" s="30" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C167" s="30" t="inlineStr">
+        <is>
+          <t>Supplier scorecards</t>
+        </is>
+      </c>
+      <c r="D167" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E167" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F167" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G167" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H167" s="30" t="inlineStr">
+        <is>
+          <t>Scorecard records</t>
+        </is>
+      </c>
+      <c r="I167" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J167" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K167" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L167" s="30" t="inlineStr">
+        <is>
+          <t>/console/procurement/scorecards</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="30" t="inlineStr">
+        <is>
+          <t>PF-030</t>
+        </is>
+      </c>
+      <c r="B168" s="30" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C168" s="30" t="inlineStr">
+        <is>
+          <t>Fabrication orders</t>
+        </is>
+      </c>
+      <c r="D168" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E168" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F168" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G168" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H168" s="30" t="inlineStr">
+        <is>
+          <t>Fabrication records</t>
+        </is>
+      </c>
+      <c r="I168" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J168" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K168" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L168" s="30" t="inlineStr">
+        <is>
+          <t>/console/production/fabrication</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="30" t="inlineStr">
+        <is>
+          <t>PF-031</t>
+        </is>
+      </c>
+      <c r="B169" s="30" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C169" s="30" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D169" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E169" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F169" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G169" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H169" s="30" t="inlineStr">
+        <is>
+          <t>Dispatch records</t>
+        </is>
+      </c>
+      <c r="I169" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J169" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K169" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L169" s="30" t="inlineStr">
+        <is>
+          <t>/console/production/dispatch + /console/production/dispatch/live + /console/production/dispatch/[dispatchId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="30" t="inlineStr">
+        <is>
+          <t>PF-032</t>
+        </is>
+      </c>
+      <c r="B170" s="30" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C170" s="30" t="inlineStr">
+        <is>
+          <t>Rentals</t>
+        </is>
+      </c>
+      <c r="D170" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E170" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F170" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G170" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H170" s="30" t="inlineStr">
+        <is>
+          <t>Rental records</t>
+        </is>
+      </c>
+      <c r="I170" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J170" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K170" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L170" s="30" t="inlineStr">
+        <is>
+          <t>/console/production/rentals + /console/production/rentals/availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="30" t="inlineStr">
+        <is>
+          <t>PF-033</t>
+        </is>
+      </c>
+      <c r="B171" s="30" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C171" s="30" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="D171" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E171" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F171" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G171" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H171" s="30" t="inlineStr">
+        <is>
+          <t>Equipment records</t>
+        </is>
+      </c>
+      <c r="I171" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J171" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K171" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L171" s="30" t="inlineStr">
+        <is>
+          <t>/console/production/equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="30" t="inlineStr">
+        <is>
+          <t>PF-034</t>
+        </is>
+      </c>
+      <c r="B172" s="30" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C172" s="30" t="inlineStr">
+        <is>
+          <t>Logistics (prod)</t>
+        </is>
+      </c>
+      <c r="D172" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E172" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F172" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G172" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H172" s="30" t="inlineStr">
+        <is>
+          <t>Production logs</t>
+        </is>
+      </c>
+      <c r="I172" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J172" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K172" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L172" s="30" t="inlineStr">
+        <is>
+          <t>/console/production/logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="30" t="inlineStr">
+        <is>
+          <t>PF-035</t>
+        </is>
+      </c>
+      <c r="B173" s="30" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C173" s="30" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="D173" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E173" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F173" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G173" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H173" s="30" t="inlineStr">
+        <is>
+          <t>Warehouse records</t>
+        </is>
+      </c>
+      <c r="I173" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J173" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K173" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L173" s="30" t="inlineStr">
+        <is>
+          <t>/console/production/warehouse + /console/production/warehouse/inventory + /console/production/warehouse/locations</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="30" t="inlineStr">
+        <is>
+          <t>PF-040</t>
+        </is>
+      </c>
+      <c r="B174" s="30" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="C174" s="30" t="inlineStr">
+        <is>
+          <t>Directory</t>
+        </is>
+      </c>
+      <c r="D174" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E174" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F174" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G174" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H174" s="30" t="inlineStr">
+        <is>
+          <t>User records</t>
+        </is>
+      </c>
+      <c r="I174" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J174" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K174" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L174" s="30" t="inlineStr">
+        <is>
+          <t>/console/people</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="30" t="inlineStr">
+        <is>
+          <t>PF-041</t>
+        </is>
+      </c>
+      <c r="B175" s="30" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="C175" s="30" t="inlineStr">
+        <is>
+          <t>Crew</t>
+        </is>
+      </c>
+      <c r="D175" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E175" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F175" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G175" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H175" s="30" t="inlineStr">
+        <is>
+          <t>Crew records</t>
+        </is>
+      </c>
+      <c r="I175" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J175" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K175" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L175" s="30" t="inlineStr">
+        <is>
+          <t>/console/people/crew</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="30" t="inlineStr">
+        <is>
+          <t>PF-042</t>
+        </is>
+      </c>
+      <c r="B176" s="30" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="C176" s="30" t="inlineStr">
+        <is>
+          <t>Credentials</t>
+        </is>
+      </c>
+      <c r="D176" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E176" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F176" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G176" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H176" s="30" t="inlineStr">
+        <is>
+          <t>Credential records</t>
+        </is>
+      </c>
+      <c r="I176" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J176" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K176" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L176" s="30" t="inlineStr">
+        <is>
+          <t>/console/people/credentials + /console/people/credentials/asset-linker</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="30" t="inlineStr">
+        <is>
+          <t>PF-043</t>
+        </is>
+      </c>
+      <c r="B177" s="30" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="C177" s="30" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="D177" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E177" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F177" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G177" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H177" s="30" t="inlineStr">
+        <is>
+          <t>Role bindings</t>
+        </is>
+      </c>
+      <c r="I177" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J177" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K177" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L177" s="30" t="inlineStr">
+        <is>
+          <t>/console/people/roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="30" t="inlineStr">
+        <is>
+          <t>PF-044</t>
+        </is>
+      </c>
+      <c r="B178" s="30" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="C178" s="30" t="inlineStr">
+        <is>
+          <t>Invites</t>
+        </is>
+      </c>
+      <c r="D178" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E178" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F178" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G178" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H178" s="30" t="inlineStr">
+        <is>
+          <t>Invite records</t>
+        </is>
+      </c>
+      <c r="I178" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J178" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K178" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L178" s="30" t="inlineStr">
+        <is>
+          <t>/console/people/invites</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="30" t="inlineStr">
+        <is>
+          <t>PF-050</t>
+        </is>
+      </c>
+      <c r="B179" s="30" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C179" s="30" t="inlineStr">
+        <is>
+          <t>AI hub</t>
+        </is>
+      </c>
+      <c r="D179" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E179" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F179" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G179" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H179" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I179" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J179" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K179" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L179" s="30" t="inlineStr">
+        <is>
+          <t>/console/ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="30" t="inlineStr">
+        <is>
+          <t>PF-051</t>
+        </is>
+      </c>
+      <c r="B180" s="30" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C180" s="30" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="D180" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E180" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F180" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G180" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H180" s="30" t="inlineStr">
+        <is>
+          <t>Conversations</t>
+        </is>
+      </c>
+      <c r="I180" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J180" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K180" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L180" s="30" t="inlineStr">
+        <is>
+          <t>/console/ai/assistant + /console/ai/assistant/[conversationId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="30" t="inlineStr">
+        <is>
+          <t>PF-052</t>
+        </is>
+      </c>
+      <c r="B181" s="30" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C181" s="30" t="inlineStr">
+        <is>
+          <t>Drafting</t>
+        </is>
+      </c>
+      <c r="D181" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E181" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F181" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G181" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H181" s="30" t="inlineStr">
+        <is>
+          <t>Drafts</t>
+        </is>
+      </c>
+      <c r="I181" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J181" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K181" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L181" s="30" t="inlineStr">
+        <is>
+          <t>/console/ai/drafting</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="30" t="inlineStr">
+        <is>
+          <t>PF-053</t>
+        </is>
+      </c>
+      <c r="B182" s="30" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C182" s="30" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D182" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E182" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F182" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G182" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H182" s="30" t="inlineStr">
+        <is>
+          <t>Agent config</t>
+        </is>
+      </c>
+      <c r="I182" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J182" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K182" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L182" s="30" t="inlineStr">
+        <is>
+          <t>/console/ai/agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="30" t="inlineStr">
+        <is>
+          <t>PF-054</t>
+        </is>
+      </c>
+      <c r="B183" s="30" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C183" s="30" t="inlineStr">
+        <is>
+          <t>Automations</t>
+        </is>
+      </c>
+      <c r="D183" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E183" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F183" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G183" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H183" s="30" t="inlineStr">
+        <is>
+          <t>Automation records</t>
+        </is>
+      </c>
+      <c r="I183" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J183" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K183" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L183" s="30" t="inlineStr">
+        <is>
+          <t>/console/ai/automations + /console/ai/automations/new + /console/ai/automations/[automationId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="30" t="inlineStr">
+        <is>
+          <t>PF-060</t>
+        </is>
+      </c>
+      <c r="B184" s="30" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="C184" s="30" t="inlineStr">
+        <is>
+          <t>Inbox</t>
+        </is>
+      </c>
+      <c r="D184" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E184" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F184" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G184" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H184" s="30" t="inlineStr">
+        <is>
+          <t>Inbox feed</t>
+        </is>
+      </c>
+      <c r="I184" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J184" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K184" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L184" s="30" t="inlineStr">
+        <is>
+          <t>/console/inbox</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="30" t="inlineStr">
+        <is>
+          <t>PF-061</t>
+        </is>
+      </c>
+      <c r="B185" s="30" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="C185" s="30" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="D185" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E185" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F185" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G185" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H185" s="30" t="inlineStr">
+        <is>
+          <t>File records</t>
+        </is>
+      </c>
+      <c r="I185" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J185" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K185" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L185" s="30" t="inlineStr">
+        <is>
+          <t>/console/files</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="30" t="inlineStr">
+        <is>
+          <t>PF-062</t>
+        </is>
+      </c>
+      <c r="B186" s="30" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="C186" s="30" t="inlineStr">
+        <is>
+          <t>Command palette</t>
+        </is>
+      </c>
+      <c r="D186" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E186" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F186" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G186" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H186" s="30" t="inlineStr">
+        <is>
+          <t>Quick actions</t>
+        </is>
+      </c>
+      <c r="I186" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J186" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K186" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L186" s="30" t="inlineStr">
+        <is>
+          <t>/console/command</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="30" t="inlineStr">
+        <is>
+          <t>PF-063</t>
+        </is>
+      </c>
+      <c r="B187" s="30" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="C187" s="30" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="D187" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E187" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F187" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G187" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H187" s="30" t="inlineStr">
+        <is>
+          <t>Form responses</t>
+        </is>
+      </c>
+      <c r="I187" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J187" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K187" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L187" s="30" t="inlineStr">
+        <is>
+          <t>/console/forms + /console/forms/new + /console/forms/[formId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="30" t="inlineStr">
+        <is>
+          <t>PF-064</t>
+        </is>
+      </c>
+      <c r="B188" s="30" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="C188" s="30" t="inlineStr">
+        <is>
+          <t>Campaigns</t>
+        </is>
+      </c>
+      <c r="D188" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E188" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F188" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G188" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H188" s="30" t="inlineStr">
+        <is>
+          <t>Campaign records</t>
+        </is>
+      </c>
+      <c r="I188" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J188" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K188" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L188" s="30" t="inlineStr">
+        <is>
+          <t>/console/campaigns</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="30" t="inlineStr">
+        <is>
+          <t>PF-070</t>
+        </is>
+      </c>
+      <c r="B189" s="30" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C189" s="30" t="inlineStr">
+        <is>
+          <t>Incidents (ops)</t>
+        </is>
+      </c>
+      <c r="D189" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E189" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F189" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G189" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H189" s="30" t="inlineStr">
+        <is>
+          <t>Incident records</t>
+        </is>
+      </c>
+      <c r="I189" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J189" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K189" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L189" s="30" t="inlineStr">
+        <is>
+          <t>/console/operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="30" t="inlineStr">
+        <is>
+          <t>PF-080</t>
+        </is>
+      </c>
+      <c r="B190" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C190" s="30" t="inlineStr">
+        <is>
+          <t>Settings hub</t>
+        </is>
+      </c>
+      <c r="D190" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E190" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F190" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G190" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H190" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I190" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J190" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K190" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L190" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="30" t="inlineStr">
+        <is>
+          <t>PF-081</t>
+        </is>
+      </c>
+      <c r="B191" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C191" s="30" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="D191" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E191" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F191" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G191" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H191" s="30" t="inlineStr">
+        <is>
+          <t>Org record</t>
+        </is>
+      </c>
+      <c r="I191" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J191" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K191" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L191" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings/organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="30" t="inlineStr">
+        <is>
+          <t>PF-082</t>
+        </is>
+      </c>
+      <c r="B192" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C192" s="30" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D192" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E192" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F192" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G192" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H192" s="30" t="inlineStr">
+        <is>
+          <t>Billing info</t>
+        </is>
+      </c>
+      <c r="I192" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J192" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K192" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L192" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings/billing</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="30" t="inlineStr">
+        <is>
+          <t>PF-083</t>
+        </is>
+      </c>
+      <c r="B193" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C193" s="30" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D193" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E193" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F193" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G193" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H193" s="30" t="inlineStr">
+        <is>
+          <t>Integration config</t>
+        </is>
+      </c>
+      <c r="I193" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J193" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K193" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L193" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings/integrations + /console/settings/integrations/marketplace + /console/settings/integrations/[integrationId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="30" t="inlineStr">
+        <is>
+          <t>PF-084</t>
+        </is>
+      </c>
+      <c r="B194" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C194" s="30" t="inlineStr">
+        <is>
+          <t>API keys</t>
+        </is>
+      </c>
+      <c r="D194" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E194" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F194" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G194" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H194" s="30" t="inlineStr">
+        <is>
+          <t>API key records</t>
+        </is>
+      </c>
+      <c r="I194" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J194" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K194" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L194" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings/api</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="30" t="inlineStr">
+        <is>
+          <t>PF-085</t>
+        </is>
+      </c>
+      <c r="B195" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C195" s="30" t="inlineStr">
+        <is>
+          <t>Webhooks</t>
+        </is>
+      </c>
+      <c r="D195" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E195" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F195" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G195" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H195" s="30" t="inlineStr">
+        <is>
+          <t>Endpoint records</t>
+        </is>
+      </c>
+      <c r="I195" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J195" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K195" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L195" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings/webhooks</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="30" t="inlineStr">
+        <is>
+          <t>PF-086</t>
+        </is>
+      </c>
+      <c r="B196" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C196" s="30" t="inlineStr">
+        <is>
+          <t>Audit log</t>
+        </is>
+      </c>
+      <c r="D196" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E196" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F196" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G196" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H196" s="30" t="inlineStr">
+        <is>
+          <t>Audit entries</t>
+        </is>
+      </c>
+      <c r="I196" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J196" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K196" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L196" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings/audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="30" t="inlineStr">
+        <is>
+          <t>PF-087</t>
+        </is>
+      </c>
+      <c r="B197" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C197" s="30" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D197" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E197" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F197" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G197" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H197" s="30" t="inlineStr">
+        <is>
+          <t>Compliance packs</t>
+        </is>
+      </c>
+      <c r="I197" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J197" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K197" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L197" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings/compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="30" t="inlineStr">
+        <is>
+          <t>PF-088</t>
+        </is>
+      </c>
+      <c r="B198" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C198" s="30" t="inlineStr">
+        <is>
+          <t>Export runs</t>
+        </is>
+      </c>
+      <c r="D198" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E198" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F198" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G198" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H198" s="30" t="inlineStr">
+        <is>
+          <t>Export records</t>
+        </is>
+      </c>
+      <c r="I198" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J198" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K198" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L198" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings/exports</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="30" t="inlineStr">
+        <is>
+          <t>PF-089</t>
+        </is>
+      </c>
+      <c r="B199" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C199" s="30" t="inlineStr">
+        <is>
+          <t>Import tools</t>
+        </is>
+      </c>
+      <c r="D199" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E199" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F199" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G199" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H199" s="30" t="inlineStr">
+        <is>
+          <t>Import runs</t>
+        </is>
+      </c>
+      <c r="I199" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J199" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K199" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L199" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings/imports</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="30" t="inlineStr">
+        <is>
+          <t>PF-090</t>
+        </is>
+      </c>
+      <c r="B200" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C200" s="30" t="inlineStr">
+        <is>
+          <t>Email templates</t>
+        </is>
+      </c>
+      <c r="D200" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E200" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F200" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G200" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H200" s="30" t="inlineStr">
+        <is>
+          <t>Template records</t>
+        </is>
+      </c>
+      <c r="I200" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J200" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K200" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L200" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings/email-templates</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="30" t="inlineStr">
+        <is>
+          <t>PF-091</t>
+        </is>
+      </c>
+      <c r="B201" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C201" s="30" t="inlineStr">
+        <is>
+          <t>Branding</t>
+        </is>
+      </c>
+      <c r="D201" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E201" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F201" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G201" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H201" s="30" t="inlineStr">
+        <is>
+          <t>Brand config</t>
+        </is>
+      </c>
+      <c r="I201" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J201" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K201" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L201" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings/branding</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="30" t="inlineStr">
+        <is>
+          <t>PF-092</t>
+        </is>
+      </c>
+      <c r="B202" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C202" s="30" t="inlineStr">
+        <is>
+          <t>Domains</t>
+        </is>
+      </c>
+      <c r="D202" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E202" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F202" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G202" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H202" s="30" t="inlineStr">
+        <is>
+          <t>Domain config</t>
+        </is>
+      </c>
+      <c r="I202" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J202" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K202" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L202" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings/domains</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="30" t="inlineStr">
+        <is>
+          <t>PF-100</t>
+        </is>
+      </c>
+      <c r="B203" s="30" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C203" s="30" t="inlineStr">
+        <is>
+          <t>My dashboard</t>
+        </is>
+      </c>
+      <c r="D203" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E203" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F203" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G203" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H203" s="30" t="inlineStr">
+        <is>
+          <t>Personal feed</t>
+        </is>
+      </c>
+      <c r="I203" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J203" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K203" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L203" s="30" t="inlineStr">
+        <is>
+          <t>/me</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="30" t="inlineStr">
+        <is>
+          <t>PF-101</t>
+        </is>
+      </c>
+      <c r="B204" s="30" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C204" s="30" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D204" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E204" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F204" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G204" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H204" s="30" t="inlineStr">
+        <is>
+          <t>User profile</t>
+        </is>
+      </c>
+      <c r="I204" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J204" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K204" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L204" s="30" t="inlineStr">
+        <is>
+          <t>/me/profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="30" t="inlineStr">
+        <is>
+          <t>PF-102</t>
+        </is>
+      </c>
+      <c r="B205" s="30" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C205" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D205" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E205" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F205" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G205" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H205" s="30" t="inlineStr">
+        <is>
+          <t>User preferences</t>
+        </is>
+      </c>
+      <c r="I205" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J205" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K205" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L205" s="30" t="inlineStr">
+        <is>
+          <t>/me/settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="30" t="inlineStr">
+        <is>
+          <t>PF-103</t>
+        </is>
+      </c>
+      <c r="B206" s="30" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C206" s="30" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="D206" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E206" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F206" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G206" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H206" s="30" t="inlineStr">
+        <is>
+          <t>Notification prefs</t>
+        </is>
+      </c>
+      <c r="I206" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J206" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K206" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L206" s="30" t="inlineStr">
+        <is>
+          <t>/me/notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="30" t="inlineStr">
+        <is>
+          <t>PF-104</t>
+        </is>
+      </c>
+      <c r="B207" s="30" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C207" s="30" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D207" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E207" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F207" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G207" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H207" s="30" t="inlineStr">
+        <is>
+          <t>Security state</t>
+        </is>
+      </c>
+      <c r="I207" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J207" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K207" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L207" s="30" t="inlineStr">
+        <is>
+          <t>/me/security</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="30" t="inlineStr">
+        <is>
+          <t>PF-105</t>
+        </is>
+      </c>
+      <c r="B208" s="30" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C208" s="30" t="inlineStr">
+        <is>
+          <t>My tickets</t>
+        </is>
+      </c>
+      <c r="D208" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E208" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F208" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G208" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H208" s="30" t="inlineStr">
+        <is>
+          <t>Ticket records</t>
+        </is>
+      </c>
+      <c r="I208" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J208" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K208" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L208" s="30" t="inlineStr">
+        <is>
+          <t>/me/tickets</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="30" t="inlineStr">
+        <is>
+          <t>PF-106</t>
+        </is>
+      </c>
+      <c r="B209" s="30" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C209" s="30" t="inlineStr">
+        <is>
+          <t>Organizations</t>
+        </is>
+      </c>
+      <c r="D209" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E209" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F209" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G209" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H209" s="30" t="inlineStr">
+        <is>
+          <t>Memberships</t>
+        </is>
+      </c>
+      <c r="I209" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J209" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K209" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L209" s="30" t="inlineStr">
+        <is>
+          <t>/me/organizations</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="30" t="inlineStr">
+        <is>
+          <t>PF-110</t>
+        </is>
+      </c>
+      <c r="B210" s="30" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C210" s="30" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D210" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E210" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F210" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G210" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H210" s="30" t="inlineStr">
+        <is>
+          <t>Home feed</t>
+        </is>
+      </c>
+      <c r="I210" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J210" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K210" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L210" s="30" t="inlineStr">
+        <is>
+          <t>/m</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="30" t="inlineStr">
+        <is>
+          <t>PF-111</t>
+        </is>
+      </c>
+      <c r="B211" s="30" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C211" s="30" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="D211" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E211" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F211" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G211" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H211" s="30" t="inlineStr">
+        <is>
+          <t>Guide content</t>
+        </is>
+      </c>
+      <c r="I211" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J211" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K211" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L211" s="30" t="inlineStr">
+        <is>
+          <t>/m/guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="30" t="inlineStr">
+        <is>
+          <t>PF-112</t>
+        </is>
+      </c>
+      <c r="B212" s="30" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C212" s="30" t="inlineStr">
+        <is>
+          <t>Tasks</t>
+        </is>
+      </c>
+      <c r="D212" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E212" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F212" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G212" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H212" s="30" t="inlineStr">
+        <is>
+          <t>Task queue</t>
+        </is>
+      </c>
+      <c r="I212" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J212" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K212" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L212" s="30" t="inlineStr">
+        <is>
+          <t>/m/tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="30" t="inlineStr">
+        <is>
+          <t>PF-113</t>
+        </is>
+      </c>
+      <c r="B213" s="30" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C213" s="30" t="inlineStr">
+        <is>
+          <t>Check-in (legacy)</t>
+        </is>
+      </c>
+      <c r="D213" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E213" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F213" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G213" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H213" s="30" t="inlineStr">
+        <is>
+          <t>Scan events</t>
+        </is>
+      </c>
+      <c r="I213" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J213" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K213" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L213" s="30" t="inlineStr">
+        <is>
+          <t>/m/check-in + /m/check-in/manual + /m/check-in/scan/[slug]</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="30" t="inlineStr">
+        <is>
+          <t>PF-114</t>
+        </is>
+      </c>
+      <c r="B214" s="30" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C214" s="30" t="inlineStr">
+        <is>
+          <t>Inventory scan</t>
+        </is>
+      </c>
+      <c r="D214" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E214" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F214" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G214" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H214" s="30" t="inlineStr">
+        <is>
+          <t>Scan events</t>
+        </is>
+      </c>
+      <c r="I214" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J214" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K214" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L214" s="30" t="inlineStr">
+        <is>
+          <t>/m/inventory/scan</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="30" t="inlineStr">
+        <is>
+          <t>PF-115</t>
+        </is>
+      </c>
+      <c r="B215" s="30" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C215" s="30" t="inlineStr">
+        <is>
+          <t>Legacy incidents</t>
+        </is>
+      </c>
+      <c r="D215" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E215" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F215" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G215" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H215" s="30" t="inlineStr">
+        <is>
+          <t>Incident records</t>
+        </is>
+      </c>
+      <c r="I215" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J215" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K215" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L215" s="30" t="inlineStr">
+        <is>
+          <t>/m/incidents/new</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="30" t="inlineStr">
+        <is>
+          <t>PF-116</t>
+        </is>
+      </c>
+      <c r="B216" s="30" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C216" s="30" t="inlineStr">
+        <is>
+          <t>Legacy crew</t>
+        </is>
+      </c>
+      <c r="D216" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E216" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F216" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G216" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H216" s="30" t="inlineStr">
+        <is>
+          <t>Clock events</t>
+        </is>
+      </c>
+      <c r="I216" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J216" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K216" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L216" s="30" t="inlineStr">
+        <is>
+          <t>/m/crew + /m/crew/clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="30" t="inlineStr">
+        <is>
+          <t>PF-117</t>
+        </is>
+      </c>
+      <c r="B217" s="30" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C217" s="30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D217" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E217" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F217" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G217" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H217" s="30" t="inlineStr">
+        <is>
+          <t>Mobile prefs</t>
+        </is>
+      </c>
+      <c r="I217" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J217" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K217" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L217" s="30" t="inlineStr">
+        <is>
+          <t>/m/settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="30" t="inlineStr">
+        <is>
+          <t>PF-120</t>
+        </is>
+      </c>
+      <c r="B218" s="30" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C218" s="30" t="inlineStr">
+        <is>
+          <t>Console overview</t>
+        </is>
+      </c>
+      <c r="D218" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E218" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F218" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G218" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H218" s="30" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="I218" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J218" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K218" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L218" s="30" t="inlineStr">
+        <is>
+          <t>/console</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="30" t="inlineStr">
+        <is>
+          <t>PF-130</t>
+        </is>
+      </c>
+      <c r="B219" s="30" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="C219" s="30" t="inlineStr">
+        <is>
+          <t>KB detail</t>
+        </is>
+      </c>
+      <c r="D219" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E219" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F219" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G219" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H219" s="30" t="inlineStr">
+        <is>
+          <t>Article body</t>
+        </is>
+      </c>
+      <c r="I219" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J219" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K219" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L219" s="30" t="inlineStr">
+        <is>
+          <t>/console/kb/[articleId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="30" t="inlineStr">
+        <is>
+          <t>PF-200</t>
+        </is>
+      </c>
+      <c r="B220" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C220" s="30" t="inlineStr">
+        <is>
+          <t>Accreditation hub</t>
+        </is>
+      </c>
+      <c r="D220" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E220" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F220" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G220" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H220" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I220" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J220" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K220" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L220" s="30" t="inlineStr">
+        <is>
+          <t>/console/accreditation + /console/accreditation/categories + /console/accreditation/zones + /console/accreditation/vetting/[applicationId] + /console/accreditation/changes/[changeId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="30" t="inlineStr">
+        <is>
+          <t>PF-201</t>
+        </is>
+      </c>
+      <c r="B221" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C221" s="30" t="inlineStr">
+        <is>
+          <t>Accommodation hub</t>
+        </is>
+      </c>
+      <c r="D221" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E221" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F221" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G221" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H221" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I221" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J221" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K221" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L221" s="30" t="inlineStr">
+        <is>
+          <t>/console/accommodation + /console/accommodation/blocks/[blockId] + /console/accommodation/village</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="30" t="inlineStr">
+        <is>
+          <t>PF-202</t>
+        </is>
+      </c>
+      <c r="B222" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C222" s="30" t="inlineStr">
+        <is>
+          <t>Commercial hub</t>
+        </is>
+      </c>
+      <c r="D222" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E222" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F222" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G222" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H222" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I222" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J222" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K222" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L222" s="30" t="inlineStr">
+        <is>
+          <t>/console/commercial + /console/commercial/brand + /console/commercial/hospitality + /console/commercial/hospitality/[packageId] + /console/commercial/licensing + /console/commercial/sponsors/[sponsorId] + /console/commercial/tickets/[ticketTypeId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="30" t="inlineStr">
+        <is>
+          <t>PF-203</t>
+        </is>
+      </c>
+      <c r="B223" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C223" s="30" t="inlineStr">
+        <is>
+          <t>Comms hub</t>
+        </is>
+      </c>
+      <c r="D223" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E223" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F223" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G223" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H223" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I223" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J223" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K223" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L223" s="30" t="inlineStr">
+        <is>
+          <t>/console/comms + /console/comms/internal/new</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="30" t="inlineStr">
+        <is>
+          <t>PF-204</t>
+        </is>
+      </c>
+      <c r="B224" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C224" s="30" t="inlineStr">
+        <is>
+          <t>Integrations hub</t>
+        </is>
+      </c>
+      <c r="D224" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E224" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F224" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G224" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H224" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I224" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J224" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K224" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L224" s="30" t="inlineStr">
+        <is>
+          <t>/console/integrations/[connectorId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="30" t="inlineStr">
+        <is>
+          <t>PF-205</t>
+        </is>
+      </c>
+      <c r="B225" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C225" s="30" t="inlineStr">
+        <is>
+          <t>Legal hub</t>
+        </is>
+      </c>
+      <c r="D225" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E225" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F225" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G225" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H225" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I225" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J225" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K225" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L225" s="30" t="inlineStr">
+        <is>
+          <t>/console/legal + /console/legal/privacy + /console/legal/privacy/datamap + /console/legal/privacy/dsar/[requestId] + /console/legal/ip/[markId] + /console/legal/privacy/consent</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="30" t="inlineStr">
+        <is>
+          <t>PF-206</t>
+        </is>
+      </c>
+      <c r="B226" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C226" s="30" t="inlineStr">
+        <is>
+          <t>Logistics hub</t>
+        </is>
+      </c>
+      <c r="D226" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E226" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F226" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G226" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H226" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I226" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J226" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K226" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L226" s="30" t="inlineStr">
+        <is>
+          <t>/console/logistics + /console/logistics/freight/[shipmentId] + /console/logistics/ratecard/[itemId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="30" t="inlineStr">
+        <is>
+          <t>PF-207</t>
+        </is>
+      </c>
+      <c r="B227" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C227" s="30" t="inlineStr">
+        <is>
+          <t>Ops / TOC hub</t>
+        </is>
+      </c>
+      <c r="D227" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E227" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F227" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G227" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H227" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I227" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J227" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K227" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L227" s="30" t="inlineStr">
+        <is>
+          <t>/console/ops + /console/ops/toc + /console/ops/toc/problems + /console/ops/toc/changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="30" t="inlineStr">
+        <is>
+          <t>PF-208</t>
+        </is>
+      </c>
+      <c r="B228" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C228" s="30" t="inlineStr">
+        <is>
+          <t>Participants hub</t>
+        </is>
+      </c>
+      <c r="D228" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E228" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F228" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G228" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H228" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I228" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J228" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K228" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L228" s="30" t="inlineStr">
+        <is>
+          <t>/console/participants + /console/participants/delegations/[delegationId] + /console/participants/visa/[caseId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="30" t="inlineStr">
+        <is>
+          <t>PF-209</t>
+        </is>
+      </c>
+      <c r="B229" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C229" s="30" t="inlineStr">
+        <is>
+          <t>Programs hub</t>
+        </is>
+      </c>
+      <c r="D229" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E229" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F229" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G229" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H229" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I229" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J229" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K229" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L229" s="30" t="inlineStr">
+        <is>
+          <t>/console/programs + /console/programs/ceremonies/[ceremonyId] + /console/programs/readiness/[exerciseId] + /console/programs/reviews/[reviewId] + /console/programs/risk/[riskId] + /console/programs/risk/new</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="30" t="inlineStr">
+        <is>
+          <t>PF-210</t>
+        </is>
+      </c>
+      <c r="B230" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C230" s="30" t="inlineStr">
+        <is>
+          <t>Safety hub</t>
+        </is>
+      </c>
+      <c r="D230" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E230" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F230" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G230" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H230" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I230" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J230" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K230" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L230" s="30" t="inlineStr">
+        <is>
+          <t>/console/safety + /console/safety/crisis/new + /console/safety/major-incident/[eventId] + /console/safety/safeguarding/[reportId] + /console/safety/medical</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="30" t="inlineStr">
+        <is>
+          <t>PF-211</t>
+        </is>
+      </c>
+      <c r="B231" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C231" s="30" t="inlineStr">
+        <is>
+          <t>Services desk hub</t>
+        </is>
+      </c>
+      <c r="D231" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E231" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F231" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G231" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H231" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I231" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J231" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K231" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L231" s="30" t="inlineStr">
+        <is>
+          <t>/console/services + /console/services/requests/[requestId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="30" t="inlineStr">
+        <is>
+          <t>PF-212</t>
+        </is>
+      </c>
+      <c r="B232" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C232" s="30" t="inlineStr">
+        <is>
+          <t>Transport hub</t>
+        </is>
+      </c>
+      <c r="D232" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E232" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F232" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G232" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H232" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I232" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J232" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K232" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L232" s="30" t="inlineStr">
+        <is>
+          <t>/console/transport + /console/transport/ad/[manifestId] + /console/transport/dispatch/[runId] + /console/transport/fleets + /console/transport/workforce</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="30" t="inlineStr">
+        <is>
+          <t>PF-213</t>
+        </is>
+      </c>
+      <c r="B233" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C233" s="30" t="inlineStr">
+        <is>
+          <t>Venues hub</t>
+        </is>
+      </c>
+      <c r="D233" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E233" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F233" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G233" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H233" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I233" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J233" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K233" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L233" s="30" t="inlineStr">
+        <is>
+          <t>/console/venues/new + /console/venues/training + /console/venues/[venueId]/zones</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="30" t="inlineStr">
+        <is>
+          <t>PF-214</t>
+        </is>
+      </c>
+      <c r="B234" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C234" s="30" t="inlineStr">
+        <is>
+          <t>Workforce hub</t>
+        </is>
+      </c>
+      <c r="D234" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E234" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F234" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G234" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H234" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I234" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J234" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K234" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L234" s="30" t="inlineStr">
+        <is>
+          <t>/console/workforce + /console/workforce/contractors/[contractorId] + /console/workforce/rosters/[rosterId] + /console/workforce/staff/[staffId] + /console/workforce/training/[courseId] + /console/workforce/volunteers/[volunteerId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="30" t="inlineStr">
+        <is>
+          <t>PF-215</t>
+        </is>
+      </c>
+      <c r="B235" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C235" s="30" t="inlineStr">
+        <is>
+          <t>Rate card (admin)</t>
+        </is>
+      </c>
+      <c r="D235" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E235" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F235" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G235" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H235" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I235" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J235" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K235" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L235" s="30" t="inlineStr">
+        <is>
+          <t>/console/ratecard</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="30" t="inlineStr">
+        <is>
+          <t>PF-216</t>
+        </is>
+      </c>
+      <c r="B236" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C236" s="30" t="inlineStr">
+        <is>
+          <t>Compliance / COC</t>
+        </is>
+      </c>
+      <c r="D236" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E236" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F236" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G236" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H236" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I236" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J236" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K236" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L236" s="30" t="inlineStr">
+        <is>
+          <t>/console/compliance/coc</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="30" t="inlineStr">
+        <is>
+          <t>PF-217</t>
+        </is>
+      </c>
+      <c r="B237" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C237" s="30" t="inlineStr">
+        <is>
+          <t>Settings · governance</t>
+        </is>
+      </c>
+      <c r="D237" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E237" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F237" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G237" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H237" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I237" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J237" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K237" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L237" s="30" t="inlineStr">
+        <is>
+          <t>/console/settings/governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="30" t="inlineStr">
+        <is>
+          <t>PF-218</t>
+        </is>
+      </c>
+      <c r="B238" s="30" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C238" s="30" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
+      <c r="D238" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E238" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F238" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G238" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H238" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I238" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J238" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K238" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L238" s="30" t="inlineStr">
+        <is>
+          <t>/console/meetings + /console/meetings/[meetingId]</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="30" t="inlineStr">
+        <is>
+          <t>PF-220</t>
+        </is>
+      </c>
+      <c r="B239" s="30" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="C239" s="30" t="inlineStr">
+        <is>
+          <t>Portal slug index</t>
+        </is>
+      </c>
+      <c r="D239" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E239" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F239" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G239" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H239" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I239" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J239" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K239" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L239" s="30" t="inlineStr">
+        <is>
+          <t>/p/[slug]</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="30" t="inlineStr">
+        <is>
+          <t>PF-221</t>
+        </is>
+      </c>
+      <c r="B240" s="30" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="C240" s="30" t="inlineStr">
+        <is>
+          <t>Portal overview (persona-agnostic)</t>
+        </is>
+      </c>
+      <c r="D240" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E240" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F240" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G240" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H240" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I240" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J240" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K240" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L240" s="30" t="inlineStr">
+        <is>
+          <t>/p/[slug]/overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="30" t="inlineStr">
+        <is>
+          <t>PF-222</t>
+        </is>
+      </c>
+      <c r="B241" s="30" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="C241" s="30" t="inlineStr">
+        <is>
+          <t>Artist portal</t>
+        </is>
+      </c>
+      <c r="D241" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E241" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F241" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G241" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H241" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I241" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J241" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K241" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L241" s="30" t="inlineStr">
+        <is>
+          <t>/p/[slug]/artist + /p/[slug]/artist/advancing + /p/[slug]/artist/catering + /p/[slug]/artist/schedule + /p/[slug]/artist/travel + /p/[slug]/artist/venue + /p/[slug]/artist/privacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="30" t="inlineStr">
+        <is>
+          <t>PF-223</t>
+        </is>
+      </c>
+      <c r="B242" s="30" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="C242" s="30" t="inlineStr">
+        <is>
+          <t>Client portal</t>
+        </is>
+      </c>
+      <c r="D242" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E242" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F242" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G242" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H242" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I242" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J242" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K242" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L242" s="30" t="inlineStr">
+        <is>
+          <t>/p/[slug]/client + /p/[slug]/client/deliverables + /p/[slug]/client/files + /p/[slug]/client/invoices + /p/[slug]/client/messages + /p/[slug]/client/proposals + /p/[slug]/client/privacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="30" t="inlineStr">
+        <is>
+          <t>PF-224</t>
+        </is>
+      </c>
+      <c r="B243" s="30" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="C243" s="30" t="inlineStr">
+        <is>
+          <t>Crew portal</t>
+        </is>
+      </c>
+      <c r="D243" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E243" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F243" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G243" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H243" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I243" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J243" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K243" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L243" s="30" t="inlineStr">
+        <is>
+          <t>/p/[slug]/crew + /p/[slug]/crew/advances + /p/[slug]/crew/call-sheet + /p/[slug]/crew/time + /p/[slug]/crew/privacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="30" t="inlineStr">
+        <is>
+          <t>PF-225</t>
+        </is>
+      </c>
+      <c r="B244" s="30" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="C244" s="30" t="inlineStr">
+        <is>
+          <t>Guest portal</t>
+        </is>
+      </c>
+      <c r="D244" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E244" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F244" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G244" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H244" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I244" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J244" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K244" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L244" s="30" t="inlineStr">
+        <is>
+          <t>/p/[slug]/guest + /p/[slug]/guest/logistics + /p/[slug]/guest/schedule + /p/[slug]/guest/tickets + /p/[slug]/guest/privacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="30" t="inlineStr">
+        <is>
+          <t>PF-226</t>
+        </is>
+      </c>
+      <c r="B245" s="30" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="C245" s="30" t="inlineStr">
+        <is>
+          <t>Sponsor portal</t>
+        </is>
+      </c>
+      <c r="D245" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E245" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F245" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G245" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H245" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I245" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J245" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K245" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L245" s="30" t="inlineStr">
+        <is>
+          <t>/p/[slug]/sponsor + /p/[slug]/sponsor/activations + /p/[slug]/sponsor/assets + /p/[slug]/sponsor/reporting + /p/[slug]/sponsor/privacy + /p/[slug]/sponsor/entitlements</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="30" t="inlineStr">
+        <is>
+          <t>PF-227</t>
+        </is>
+      </c>
+      <c r="B246" s="30" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="C246" s="30" t="inlineStr">
+        <is>
+          <t>Vendor portal</t>
+        </is>
+      </c>
+      <c r="D246" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E246" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F246" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G246" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H246" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I246" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J246" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K246" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L246" s="30" t="inlineStr">
+        <is>
+          <t>/p/[slug]/vendor + /p/[slug]/vendor/credentials + /p/[slug]/vendor/equipment-pull-list + /p/[slug]/vendor/invoices + /p/[slug]/vendor/purchase-orders + /p/[slug]/vendor/submissions + /p/[slug]/vendor/privacy + /p/[slug]/vendor/training</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="30" t="inlineStr">
+        <is>
+          <t>PF-228</t>
+        </is>
+      </c>
+      <c r="B247" s="30" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="C247" s="30" t="inlineStr">
+        <is>
+          <t>Guide (Boarding Pass)</t>
+        </is>
+      </c>
+      <c r="D247" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E247" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F247" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G247" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H247" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I247" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J247" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K247" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L247" s="30" t="inlineStr">
+        <is>
+          <t>/p/[slug]/guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="30" t="inlineStr">
+        <is>
+          <t>PF-300</t>
+        </is>
+      </c>
+      <c r="B248" s="30" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="C248" s="30" t="inlineStr">
+        <is>
+          <t>Public site</t>
+        </is>
+      </c>
+      <c r="D248" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E248" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F248" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G248" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H248" s="30" t="inlineStr">
+        <is>
+          <t>Marketing content</t>
+        </is>
+      </c>
+      <c r="I248" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J248" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K248" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L248" s="30" t="inlineStr">
+        <is>
+          <t>/ + /pricing + /features + /about + /contact + /docs + /blog + /changelog</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="30" t="inlineStr">
+        <is>
+          <t>PF-301</t>
+        </is>
+      </c>
+      <c r="B249" s="30" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="C249" s="30" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="D249" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E249" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F249" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G249" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H249" s="30" t="inlineStr">
+        <is>
+          <t>Marketing content</t>
+        </is>
+      </c>
+      <c r="I249" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J249" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K249" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L249" s="30" t="inlineStr">
+        <is>
+          <t>/solutions + /solutions/[industry] + /solutions/atlvs + /solutions/gvteway + /solutions/compvss</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="30" t="inlineStr">
+        <is>
+          <t>PF-302</t>
+        </is>
+      </c>
+      <c r="B250" s="30" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="C250" s="30" t="inlineStr">
+        <is>
+          <t>Feature modules</t>
+        </is>
+      </c>
+      <c r="D250" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E250" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F250" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G250" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H250" s="30" t="inlineStr">
+        <is>
+          <t>Marketing content</t>
+        </is>
+      </c>
+      <c r="I250" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J250" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K250" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L250" s="30" t="inlineStr">
+        <is>
+          <t>/features/[module]</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="30" t="inlineStr">
+        <is>
+          <t>PF-303</t>
+        </is>
+      </c>
+      <c r="B251" s="30" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="C251" s="30" t="inlineStr">
+        <is>
+          <t>Case studies</t>
+        </is>
+      </c>
+      <c r="D251" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E251" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F251" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G251" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H251" s="30" t="inlineStr">
+        <is>
+          <t>Case study content</t>
+        </is>
+      </c>
+      <c r="I251" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J251" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K251" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L251" s="30" t="inlineStr">
+        <is>
+          <t>/customers + /customers/[slug]</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="30" t="inlineStr">
+        <is>
+          <t>PF-304</t>
+        </is>
+      </c>
+      <c r="B252" s="30" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="C252" s="30" t="inlineStr">
+        <is>
+          <t>Blog posts</t>
+        </is>
+      </c>
+      <c r="D252" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E252" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F252" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G252" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H252" s="30" t="inlineStr">
+        <is>
+          <t>Blog content</t>
+        </is>
+      </c>
+      <c r="I252" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J252" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K252" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L252" s="30" t="inlineStr">
+        <is>
+          <t>/blog/[slug]</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="30" t="inlineStr">
+        <is>
+          <t>PF-305</t>
+        </is>
+      </c>
+      <c r="B253" s="30" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="C253" s="30" t="inlineStr">
+        <is>
+          <t>Legal pages</t>
+        </is>
+      </c>
+      <c r="D253" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E253" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F253" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G253" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H253" s="30" t="inlineStr">
+        <is>
+          <t>Legal content</t>
+        </is>
+      </c>
+      <c r="I253" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J253" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K253" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L253" s="30" t="inlineStr">
+        <is>
+          <t>/legal/terms + /legal/privacy + /legal/dpa + /legal/sla</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="30" t="inlineStr">
+        <is>
+          <t>PF-400</t>
+        </is>
+      </c>
+      <c r="B254" s="30" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C254" s="30" t="inlineStr">
+        <is>
+          <t>Sign in</t>
+        </is>
+      </c>
+      <c r="D254" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E254" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F254" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G254" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H254" s="30" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="I254" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J254" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K254" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L254" s="30" t="inlineStr">
+        <is>
+          <t>/login</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="30" t="inlineStr">
+        <is>
+          <t>PF-401</t>
+        </is>
+      </c>
+      <c r="B255" s="30" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C255" s="30" t="inlineStr">
+        <is>
+          <t>Sign up</t>
+        </is>
+      </c>
+      <c r="D255" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E255" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F255" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G255" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H255" s="30" t="inlineStr">
+        <is>
+          <t>User account</t>
+        </is>
+      </c>
+      <c r="I255" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J255" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K255" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L255" s="30" t="inlineStr">
+        <is>
+          <t>/signup</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="30" t="inlineStr">
+        <is>
+          <t>PF-402</t>
+        </is>
+      </c>
+      <c r="B256" s="30" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C256" s="30" t="inlineStr">
+        <is>
+          <t>Forgot password</t>
+        </is>
+      </c>
+      <c r="D256" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E256" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F256" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G256" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H256" s="30" t="inlineStr">
+        <is>
+          <t>Reset email</t>
+        </is>
+      </c>
+      <c r="I256" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J256" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K256" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L256" s="30" t="inlineStr">
+        <is>
+          <t>/forgot-password + /reset-password + /reset-password/[token]</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="30" t="inlineStr">
+        <is>
+          <t>PF-403</t>
+        </is>
+      </c>
+      <c r="B257" s="30" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C257" s="30" t="inlineStr">
+        <is>
+          <t>Email verification</t>
+        </is>
+      </c>
+      <c r="D257" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E257" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F257" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G257" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H257" s="30" t="inlineStr">
+        <is>
+          <t>Verified flag</t>
+        </is>
+      </c>
+      <c r="I257" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J257" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K257" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L257" s="30" t="inlineStr">
+        <is>
+          <t>/verify-email + /verify-email/[token]</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="30" t="inlineStr">
+        <is>
+          <t>PF-404</t>
+        </is>
+      </c>
+      <c r="B258" s="30" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C258" s="30" t="inlineStr">
+        <is>
+          <t>Magic link</t>
+        </is>
+      </c>
+      <c r="D258" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E258" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F258" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G258" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H258" s="30" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="I258" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J258" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K258" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L258" s="30" t="inlineStr">
+        <is>
+          <t>/magic-link/[token]</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="30" t="inlineStr">
+        <is>
+          <t>PF-405</t>
+        </is>
+      </c>
+      <c r="B259" s="30" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C259" s="30" t="inlineStr">
+        <is>
+          <t>Accept invite</t>
+        </is>
+      </c>
+      <c r="D259" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E259" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F259" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G259" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H259" s="30" t="inlineStr">
+        <is>
+          <t>Membership</t>
+        </is>
+      </c>
+      <c r="I259" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J259" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K259" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L259" s="30" t="inlineStr">
+        <is>
+          <t>/accept-invite/[token]</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="30" t="inlineStr">
+        <is>
+          <t>PF-406</t>
+        </is>
+      </c>
+      <c r="B260" s="30" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C260" s="30" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
+      </c>
+      <c r="D260" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E260" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F260" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G260" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H260" s="30" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="I260" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J260" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K260" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L260" s="30" t="inlineStr">
+        <is>
+          <t>/sso/[provider]</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="30" t="inlineStr">
+        <is>
+          <t>PF-407</t>
+        </is>
+      </c>
+      <c r="B261" s="30" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C261" s="30" t="inlineStr">
+        <is>
+          <t>Proposals public</t>
+        </is>
+      </c>
+      <c r="D261" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E261" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F261" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G261" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H261" s="30" t="inlineStr">
+        <is>
+          <t>Signed proposal</t>
+        </is>
+      </c>
+      <c r="I261" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J261" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K261" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L261" s="30" t="inlineStr">
+        <is>
+          <t>/proposals/[token]</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="30" t="inlineStr">
+        <is>
+          <t>PF-408</t>
+        </is>
+      </c>
+      <c r="B262" s="30" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C262" s="30" t="inlineStr">
+        <is>
+          <t>Site artifacts</t>
+        </is>
+      </c>
+      <c r="D262" s="30" t="inlineStr">
+        <is>
+          <t>XG</t>
+        </is>
+      </c>
+      <c r="E262" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F262" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G262" s="43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H262" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I262" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J262" s="30" t="inlineStr">
+        <is>
+          <t>Platform baseline — pre-Olympic FBW capability.</t>
+        </is>
+      </c>
+      <c r="K262" s="44" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="L262" s="30" t="inlineStr">
+        <is>
+          <t>/og + /robots.txt + /sitemap.xml</t>
         </is>
       </c>
     </row>
